--- a/MainTop/17.08.2026 имена гор/Воронеж_print_sorted.xlsx
+++ b/MainTop/17.08.2026 имена гор/Воронеж_print_sorted.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L2" s="1" t="n">
@@ -590,7 +590,7 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L3" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L4" s="1" t="n">
@@ -702,7 +702,7 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L5" s="1" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L6" s="1" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L7" s="1" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L8" s="1" t="n">
@@ -926,7 +926,7 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L9" s="1" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L10" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L11" s="1" t="n">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L12" s="1" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L13" s="1" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L14" s="1" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L15" s="1" t="n">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L16" s="1" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L17" s="1" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L18" s="1" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>спрос</t>
+          <t>17.08.2026 имена гор</t>
         </is>
       </c>
       <c r="L19" s="1" t="n">
